--- a/data/upload/packing/TJ-25-26-183.xlsx
+++ b/data/upload/packing/TJ-25-26-183.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\TJ-25-26-183 NE ( Franklin Farms )\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BEB8BA-6C85-4353-B8DE-55AFD378FFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A8F50E-8E78-4E06-9F00-22FFAA33BB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6535,6 +6535,11 @@
     <filterColumn colId="6">
       <filters blank="1"/>
     </filterColumn>
+    <filterColumn colId="11">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
   </autoFilter>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Project Code" dataDxfId="22"/>
@@ -6861,11 +6866,11 @@
     <row r="1" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P1">
         <f>SUBTOTAL(9,NavDataRegion[Total Qty])</f>
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q1" s="2">
         <f>SUBTOTAL(9,NavDataRegion[Total Wt])</f>
-        <v>14782.178771973999</v>
+        <v>716.35419999999999</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -55496,7 +55501,7 @@
       <c r="U794" s="3"/>
       <c r="V794" s="3"/>
     </row>
-    <row r="795" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="3" t="s">
         <v>11</v>
       </c>
@@ -55547,7 +55552,7 @@
       <c r="U795" s="3"/>
       <c r="V795" s="3"/>
     </row>
-    <row r="796" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="3" t="s">
         <v>11</v>
       </c>
@@ -55657,7 +55662,7 @@
       <c r="U797" s="3"/>
       <c r="V797" s="3"/>
     </row>
-    <row r="798" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="3" t="s">
         <v>11</v>
       </c>
@@ -56121,7 +56126,7 @@
       <c r="U805" s="3"/>
       <c r="V805" s="3"/>
     </row>
-    <row r="806" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="3" t="s">
         <v>11</v>
       </c>
@@ -56172,7 +56177,7 @@
       <c r="U806" s="3"/>
       <c r="V806" s="3"/>
     </row>
-    <row r="807" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="3" t="s">
         <v>11</v>
       </c>
@@ -57633,7 +57638,7 @@
       <c r="U831" s="3"/>
       <c r="V831" s="3"/>
     </row>
-    <row r="832" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="3" t="s">
         <v>11</v>
       </c>
@@ -57684,7 +57689,7 @@
       <c r="U832" s="3"/>
       <c r="V832" s="3"/>
     </row>
-    <row r="833" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="3" t="s">
         <v>11</v>
       </c>
@@ -57735,7 +57740,7 @@
       <c r="U833" s="3"/>
       <c r="V833" s="3"/>
     </row>
-    <row r="834" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="3" t="s">
         <v>11</v>
       </c>
@@ -57786,7 +57791,7 @@
       <c r="U834" s="3"/>
       <c r="V834" s="3"/>
     </row>
-    <row r="835" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="3" t="s">
         <v>11</v>
       </c>
@@ -57837,7 +57842,7 @@
       <c r="U835" s="3"/>
       <c r="V835" s="3"/>
     </row>
-    <row r="836" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="3" t="s">
         <v>11</v>
       </c>
@@ -57888,7 +57893,7 @@
       <c r="U836" s="3"/>
       <c r="V836" s="3"/>
     </row>
-    <row r="837" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="3" t="s">
         <v>11</v>
       </c>
@@ -58287,7 +58292,7 @@
       <c r="U843" s="3"/>
       <c r="V843" s="3"/>
     </row>
-    <row r="844" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:22" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="3" t="s">
         <v>11</v>
       </c>
